--- a/テーブル仕様書.xlsx
+++ b/テーブル仕様書.xlsx
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>enum('in_progress','overdue','completed')</t>
+          <t>enum('in_progress','completed','expired')</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr"/>
@@ -1866,7 +1866,7 @@
         <is>
           <t>新規読書計画作成時：進行中
 読了するボタン押下後：完了
-設定した期日を超過：期限超過</t>
+設定した期日を超過：期限切れ</t>
         </is>
       </c>
     </row>

--- a/テーブル仕様書.xlsx
+++ b/テーブル仕様書.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -601,7 +601,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
@@ -887,11 +887,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr"/>
     </row>
@@ -909,7 +905,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>varchar(1000)</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
@@ -931,7 +927,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>varchar(2048)</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
@@ -1065,7 +1061,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
@@ -1124,7 +1120,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>book_genresテーブル</t>
+          <t>book_genreテーブル</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1362,7 +1358,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>tinyint unsigned</t>
+          <t>tinyint</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
@@ -1388,11 +1384,15 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="3" t="inlineStr"/>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>ユーザーID</t>
+          <t>お気に入りID</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>○(book_idとの組み合わせ)</t>
+          <t>○</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -1471,27 +1471,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>users(id)</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>削除時：CASCADE</t>
-        </is>
-      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>書籍ID</t>
+          <t>ユーザーID</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -1499,11 +1491,7 @@
           <t>bigint unsigned</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>○(user_idとの組み合わせ)</t>
-        </is>
-      </c>
+      <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
           <t>○</t>
@@ -1511,12 +1499,13 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>books(id)</t>
+          <t>users(id)</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>削除時：CASCADE</t>
+          <t>user_id, book_idでUNIQUE
+削除時：CASCADE</t>
         </is>
       </c>
     </row>
@@ -1524,34 +1513,46 @@
       <c r="A42" s="4" t="n"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
+          <t>book_id</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>書籍ID</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>bigint unsigned</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>books(id)</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>削除時：CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>作成日</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>更新日</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -1564,68 +1565,52 @@
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>更新日</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>review_likesテーブル</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>review_id</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>レビューID</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>レビューいいねID</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>bigint unsigned</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>○(user_idとの組み合わせ)</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>reviews(id)</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>削除時：CASCADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n"/>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>bigint unsigned</t>
-        </is>
-      </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>○(review_idとの組み合わせ)</t>
+          <t>○</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -1633,178 +1618,171 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>users(id)</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>削除時：CASCADE</t>
-        </is>
-      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
+          <t>review_id</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>レビューID</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>bigint unsigned</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>reviews(id)</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>削除時：CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>ユーザーID</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>bigint unsigned</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>users(id)</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>user_id, review_idでUNIQUE
+削除時：CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>作成日</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="n"/>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>更新日</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>reading_plansテーブル</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>読書計画ID</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>bigint unsigned</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="3" t="inlineStr"/>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="n"/>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>book_id</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>書籍ID</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>reading_plansテーブル</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>読書計画ID</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>bigint unsigned</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>books(id)</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>削除時：CASCADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>bigint unsigned</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>users(id)</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>削除時：CASCADE</t>
-        </is>
-      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>target_date</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>期日</t>
+          <t>書籍ID</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>bigint unsigned</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr"/>
@@ -1813,46 +1791,67 @@
           <t>○</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>books(id)</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>削除時：CASCADE</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>完了日</t>
+          <t>ユーザーID</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>bigint unsigned</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>users(id)</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>user_id, statusでINDEX
+削除時：CASCADE</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>target_date</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>期日</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>enum('in_progress','completed','expired')</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr"/>
@@ -1864,9 +1863,7 @@
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>新規読書計画作成時：進行中
-読了するボタン押下後：完了
-設定した期日を超過：期限切れ</t>
+          <t>INDEX</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1871,12 @@
       <c r="A56" s="4" t="n"/>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>completed_at</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>作成日</t>
+          <t>完了日</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -1893,136 +1890,131 @@
       <c r="H56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n"/>
+      <c r="A57" s="4" t="n"/>
       <c r="B57" s="3" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>enum('in_progress','completed','expired')</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>新規読書計画作成時：進行中
+読了するボタン押下後：完了
+設定した期日を超過：期限切れ
+デフォルト：in_progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n"/>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>作成日</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>更新日</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>notificationsテーブル</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>通知ID</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr"/>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="n"/>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>通知クラス名</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>どの種類の通知かを判別するのに利用</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
-      <c r="A61" s="4" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>notificationsテーブル</t>
+        </is>
+      </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>notifiable_type</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>モデル種類</t>
+          <t>通知ID</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr"/>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>通知を受け取るモデルの種類（クラス名）</t>
-        </is>
-      </c>
+      <c r="H61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>notifiable_id</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>インスタンスID</t>
+          <t>通知クラス名</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>bigint unsigned</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr"/>
@@ -2034,7 +2026,7 @@
       <c r="G62" s="3" t="inlineStr"/>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>通知を受け取るユーザーID</t>
+          <t>どの種類の通知かを判別するのに利用</t>
         </is>
       </c>
     </row>
@@ -2042,17 +2034,17 @@
       <c r="A63" s="4" t="n"/>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>notifiable_type</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>通知データ</t>
+          <t>モデル種類</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>text(json)</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr"/>
@@ -2062,62 +2054,79 @@
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>通知を受け取るモデルの種類（クラス名）
+notifiable_type, notifiable_idでINDEX</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n"/>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>read_at</t>
+          <t>notifiable_id</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>既読日時</t>
+          <t>インスタンスID</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>bigint unsigned</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>通知を受け取るユーザーID</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>作成日</t>
+          <t>通知データ</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="G65" s="3" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n"/>
+      <c r="A66" s="4" t="n"/>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>read_at</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>更新日</t>
+          <t>既読日時</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -2130,16 +2139,60 @@
       <c r="G66" s="3" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" s="4" t="n"/>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>作成日</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>更新日</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="A32:A38"/>
     <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="A61:A68"/>
     <mergeCell ref="A2:A9"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="A59:A66"/>
+    <mergeCell ref="A52:A59"/>
     <mergeCell ref="A11:A20"/>
-    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A46:A50"/>
     <mergeCell ref="A22:A25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/テーブル仕様書.xlsx
+++ b/テーブル仕様書.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1071,7 +1071,11 @@
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -2183,17 +2187,570 @@
       <c r="G68" s="3" t="inlineStr"/>
       <c r="H68" s="3" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>password_reset_tokensテーブル</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>メールアドレス</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>varchar(255)</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n"/>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>トークン</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>varchar(255)</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>パスワードリセット用（ハッシュ化して保存）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>作成日</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>personal_access_tokensテーブル</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>トークンID</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>bigint unsigned</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n"/>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>tokenable_type</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>トークン所有者の種類</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>varchar(255)</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>トークンを持つモデルの種類（クラス名）
+tokenable_type, tokenable_idでINDEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n"/>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>tokenable_id</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>トークン所有者のID</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>bigint unsigned</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>トークンを持つユーザーID
+tokenable_type, tokenable_idでINDEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n"/>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>トークン名</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>varchar(255)</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n"/>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>トークン</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>varchar(64)</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>UNIQUE（ハッシュ化して保存）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n"/>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>abilities</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>トークンに許可する操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n"/>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>last_used_at</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>最終使用日時</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n"/>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>expires_at</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>有効期限</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n"/>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n"/>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>作成日</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>更新日</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>failed_jobsテーブル</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>失敗ジョブID</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>bigint unsigned</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n"/>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>ジョブUUID</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>varchar(255)</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n"/>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>connection</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>接続名</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n"/>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>queue</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>キュー名</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n"/>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>ジョブ内容</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>longtext</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n"/>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>例外内容</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>longtext</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>failed_at</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>失敗日時</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト：現在日時</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
     <mergeCell ref="A40:A44"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A70:A72"/>
     <mergeCell ref="A61:A68"/>
     <mergeCell ref="A2:A9"/>
     <mergeCell ref="A52:A59"/>
+    <mergeCell ref="A85:A91"/>
     <mergeCell ref="A11:A20"/>
     <mergeCell ref="A46:A50"/>
     <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A74:A83"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/テーブル仕様書.xlsx
+++ b/テーブル仕様書.xlsx
@@ -1197,7 +1197,8 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>削除時：RESTRICT（使用中のジャンルは削除不可）</t>
+          <t>削除時：CASCADE
+※書籍に紐づいているジャンルの削除は、アプリ側（GenreController@destroy）で事前に判定して中止する</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1389,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr"/>
@@ -1398,7 +1399,11 @@
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>文字数はバリデーション（ReviewRequest）で255文字以内に制限</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -1907,7 +1912,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>enum('in_progress','completed','expired')</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr"/>
@@ -1919,7 +1924,9 @@
       <c r="G57" s="3" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>新規読書計画作成時：進行中
+          <t>値：in_progress（進行中）/ completed（完了）/ expired（期限切れ）
+ReadingPlanStatus Enum でキャストする
+新規読書計画作成時：進行中
 読了するボタン押下後：完了
 設定した期日を超過：期限切れ
 デフォルト：in_progress</t>

--- a/テーブル仕様書.xlsx
+++ b/テーブル仕様書.xlsx
@@ -2226,7 +2226,11 @@
         </is>
       </c>
       <c r="G70" s="3" t="n"/>
-      <c r="H70" s="3" t="n"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Laravel標準のテーブル。本アプリではパスワードリセット機能を使っていないため未使用</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n"/>
@@ -2312,7 +2316,11 @@
         </is>
       </c>
       <c r="G74" s="3" t="n"/>
-      <c r="H74" s="3" t="n"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Laravel Sanctum のテーブル。公開APIのBearerトークン認証で使用</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
@@ -2578,7 +2586,11 @@
         </is>
       </c>
       <c r="G85" s="3" t="n"/>
-      <c r="H85" s="3" t="n"/>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>Laravel標準のテーブル。本アプリではキューを使っていないため未使用</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n"/>

--- a/テーブル仕様書.xlsx
+++ b/テーブル仕様書.xlsx
@@ -1995,7 +1995,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>UUID</t>
+          <t>char(36)（UUID）</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>varchar</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr"/>
